--- a/AlleLernwortschatze.xlsx
+++ b/AlleLernwortschatze.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoms\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoms\PycharmProjects\articlesGermanA1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61A5E38-B440-4389-AE03-28A145BE369E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED299BF0-C149-477B-9CF5-B101B014EB84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="8496" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2244" yWindow="636" windowWidth="13392" windowHeight="11148" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit 1 + 2" sheetId="1" r:id="rId1"/>
     <sheet name="Unit 3" sheetId="5" r:id="rId2"/>
     <sheet name="Unit 4" sheetId="4" r:id="rId3"/>
-    <sheet name="die Körperteile" sheetId="6" r:id="rId4"/>
-    <sheet name="das Haus und die Möbel" sheetId="7" r:id="rId5"/>
+    <sheet name="Die Kleidung" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="760">
   <si>
     <t>Artikel</t>
   </si>
@@ -135,9 +134,6 @@
     <t>Koffer</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>ˈkɔfɐ</t>
   </si>
   <si>
@@ -216,9 +212,6 @@
     <t>Schweiz</t>
   </si>
   <si>
-    <t>-----</t>
-  </si>
-  <si>
     <t>ʃvaɪ̯t͡s</t>
   </si>
   <si>
@@ -2043,401 +2036,293 @@
     <t>Joghurt (Österreich)</t>
   </si>
   <si>
-    <t>Kopf</t>
-  </si>
-  <si>
-    <t>Köpfe</t>
-  </si>
-  <si>
-    <t>head</t>
-  </si>
-  <si>
-    <t>Gesicht</t>
-  </si>
-  <si>
-    <t>Gesichter</t>
-  </si>
-  <si>
-    <t>face</t>
-  </si>
-  <si>
-    <t>Haar</t>
-  </si>
-  <si>
-    <t>Haare</t>
-  </si>
-  <si>
-    <t>hair</t>
-  </si>
-  <si>
-    <t>Auge</t>
-  </si>
-  <si>
-    <t>Augen</t>
-  </si>
-  <si>
-    <t>eye</t>
-  </si>
-  <si>
-    <t>Nase</t>
-  </si>
-  <si>
-    <t>Nasen</t>
-  </si>
-  <si>
-    <t>nose</t>
-  </si>
-  <si>
-    <t>Mund</t>
-  </si>
-  <si>
-    <t>Münder</t>
-  </si>
-  <si>
-    <t>mouth</t>
-  </si>
-  <si>
-    <t>Zahn</t>
-  </si>
-  <si>
-    <t>Zähne</t>
-  </si>
-  <si>
-    <t>tooth</t>
-  </si>
-  <si>
-    <t>Ohr</t>
-  </si>
-  <si>
-    <t>Ohren</t>
-  </si>
-  <si>
-    <t>ear</t>
-  </si>
-  <si>
-    <t>Hals</t>
-  </si>
-  <si>
-    <t>Hälse</t>
-  </si>
-  <si>
-    <t>neck / throat</t>
-  </si>
-  <si>
-    <t>Schulter</t>
-  </si>
-  <si>
-    <t>Schultern</t>
-  </si>
-  <si>
-    <t>shoulder</t>
-  </si>
-  <si>
-    <t>Arm</t>
-  </si>
-  <si>
-    <t>Arme</t>
-  </si>
-  <si>
-    <t>arm</t>
-  </si>
-  <si>
-    <t>Hand</t>
-  </si>
-  <si>
-    <t>Hände</t>
-  </si>
-  <si>
-    <t>hand</t>
-  </si>
-  <si>
-    <t>Finger</t>
-  </si>
-  <si>
-    <t>finger</t>
-  </si>
-  <si>
-    <t>Brust</t>
-  </si>
-  <si>
-    <t>Brüste</t>
-  </si>
-  <si>
-    <t>chest / breast</t>
-  </si>
-  <si>
-    <t>Bauch</t>
-  </si>
-  <si>
-    <t>Bäuche</t>
-  </si>
-  <si>
-    <t>stomach / belly</t>
-  </si>
-  <si>
-    <t>Rücken</t>
-  </si>
-  <si>
-    <t>back</t>
-  </si>
-  <si>
-    <t>Bein</t>
-  </si>
-  <si>
-    <t>Beine</t>
-  </si>
-  <si>
-    <t>leg</t>
-  </si>
-  <si>
-    <t>Knie</t>
-  </si>
-  <si>
-    <t>knee</t>
-  </si>
-  <si>
-    <t>Fuß</t>
-  </si>
-  <si>
-    <t>Füße</t>
-  </si>
-  <si>
-    <t>foot</t>
-  </si>
-  <si>
-    <t>Zehe</t>
-  </si>
-  <si>
-    <t>Zehen</t>
-  </si>
-  <si>
-    <t>toe</t>
-  </si>
-  <si>
-    <t>room</t>
-  </si>
-  <si>
-    <t>Wohnzimmer</t>
-  </si>
-  <si>
-    <t>living room</t>
-  </si>
-  <si>
-    <t>Schlafzimmer</t>
-  </si>
-  <si>
-    <t>bedroom</t>
-  </si>
-  <si>
-    <t>Küche</t>
-  </si>
-  <si>
-    <t>Küchen</t>
-  </si>
-  <si>
-    <t>kitchen</t>
-  </si>
-  <si>
-    <t>Badezimmer</t>
-  </si>
-  <si>
-    <t>bathroom</t>
-  </si>
-  <si>
-    <t>Esszimmer</t>
-  </si>
-  <si>
-    <t>dining room</t>
-  </si>
-  <si>
-    <t>Flur</t>
-  </si>
-  <si>
-    <t>Flure</t>
-  </si>
-  <si>
-    <t>hallway</t>
-  </si>
-  <si>
-    <t>Balkon</t>
-  </si>
-  <si>
-    <t>Balkone</t>
-  </si>
-  <si>
-    <t>balcony</t>
-  </si>
-  <si>
-    <t>Garten</t>
-  </si>
-  <si>
-    <t>Gärten</t>
-  </si>
-  <si>
-    <t>garden</t>
-  </si>
-  <si>
-    <t>Keller</t>
-  </si>
-  <si>
-    <t>basement / cellar</t>
-  </si>
-  <si>
-    <t>table</t>
-  </si>
-  <si>
-    <t>chair</t>
-  </si>
-  <si>
-    <t>Sessel</t>
-  </si>
-  <si>
-    <t>armchair</t>
-  </si>
-  <si>
-    <t>Sofa</t>
-  </si>
-  <si>
-    <t>Sofas</t>
-  </si>
-  <si>
-    <t>sofa</t>
-  </si>
-  <si>
-    <t>Bett</t>
-  </si>
-  <si>
-    <t>Betten</t>
-  </si>
-  <si>
-    <t>bed</t>
-  </si>
-  <si>
-    <t>Schrank</t>
-  </si>
-  <si>
-    <t>Schränke</t>
-  </si>
-  <si>
-    <t>wardrobe / cabinet</t>
-  </si>
-  <si>
-    <t>Regal</t>
-  </si>
-  <si>
-    <t>Regale</t>
-  </si>
-  <si>
-    <t>shelf</t>
-  </si>
-  <si>
-    <t>Teppich</t>
-  </si>
-  <si>
-    <t>Teppiche</t>
-  </si>
-  <si>
-    <t>rug / carpet</t>
-  </si>
-  <si>
-    <t>picture</t>
-  </si>
-  <si>
-    <t>Lampe</t>
-  </si>
-  <si>
-    <t>Lampen</t>
-  </si>
-  <si>
-    <t>lamp</t>
-  </si>
-  <si>
-    <t>Tür</t>
-  </si>
-  <si>
-    <t>Türen</t>
-  </si>
-  <si>
-    <t>door</t>
-  </si>
-  <si>
-    <t>Fenster</t>
-  </si>
-  <si>
-    <t>window</t>
-  </si>
-  <si>
-    <t>Spiegel</t>
-  </si>
-  <si>
-    <t>mirror</t>
-  </si>
-  <si>
-    <t>Uhr</t>
-  </si>
-  <si>
-    <t>Uhren</t>
-  </si>
-  <si>
-    <t>clock</t>
-  </si>
-  <si>
-    <t>Fernseher</t>
-  </si>
-  <si>
-    <t>television</t>
-  </si>
-  <si>
-    <t>Kühlschrank</t>
-  </si>
-  <si>
-    <t>Kühlschränke</t>
-  </si>
-  <si>
-    <t>refrigerator</t>
-  </si>
-  <si>
-    <t>Herd</t>
-  </si>
-  <si>
-    <t>Herde</t>
-  </si>
-  <si>
-    <t>stove</t>
-  </si>
-  <si>
-    <t>Dusche</t>
-  </si>
-  <si>
-    <t>Duschen</t>
-  </si>
-  <si>
-    <t>shower</t>
-  </si>
-  <si>
-    <t>Badewanne</t>
-  </si>
-  <si>
-    <t>Badewannen</t>
-  </si>
-  <si>
-    <t>bathtub</t>
-  </si>
-  <si>
-    <t>Schreibtisch</t>
-  </si>
-  <si>
-    <t>Schreibtische</t>
-  </si>
-  <si>
-    <t>desk</t>
+    <t>Der</t>
+  </si>
+  <si>
+    <t>Pullover</t>
+  </si>
+  <si>
+    <t>Sweater</t>
+  </si>
+  <si>
+    <t>Mantel</t>
+  </si>
+  <si>
+    <t>Mäntel</t>
+  </si>
+  <si>
+    <t>Coat</t>
+  </si>
+  <si>
+    <t>Rock</t>
+  </si>
+  <si>
+    <t>Röcke</t>
+  </si>
+  <si>
+    <t>Skirt</t>
+  </si>
+  <si>
+    <t>Anzug</t>
+  </si>
+  <si>
+    <t>Anzüge</t>
+  </si>
+  <si>
+    <t>Suit</t>
+  </si>
+  <si>
+    <t>Schal</t>
+  </si>
+  <si>
+    <t>Schals</t>
+  </si>
+  <si>
+    <t>Scarf</t>
+  </si>
+  <si>
+    <t>Gürtel</t>
+  </si>
+  <si>
+    <t>Belt</t>
+  </si>
+  <si>
+    <t>Hut</t>
+  </si>
+  <si>
+    <t>Hüte</t>
+  </si>
+  <si>
+    <t>Hat</t>
+  </si>
+  <si>
+    <t>Handschuh</t>
+  </si>
+  <si>
+    <t>Handschuhe</t>
+  </si>
+  <si>
+    <t>Glove</t>
+  </si>
+  <si>
+    <t>Schuh</t>
+  </si>
+  <si>
+    <t>Schuhe</t>
+  </si>
+  <si>
+    <t>Shoe</t>
+  </si>
+  <si>
+    <t>Stiefel</t>
+  </si>
+  <si>
+    <t>Boots</t>
+  </si>
+  <si>
+    <t>Turnschuh</t>
+  </si>
+  <si>
+    <t>Turnschuhe</t>
+  </si>
+  <si>
+    <t>Trainer</t>
+  </si>
+  <si>
+    <t>Die</t>
+  </si>
+  <si>
+    <t>Hose</t>
+  </si>
+  <si>
+    <t>Hosen</t>
+  </si>
+  <si>
+    <t>Trousers</t>
+  </si>
+  <si>
+    <t>Jeans</t>
+  </si>
+  <si>
+    <t>Jacke</t>
+  </si>
+  <si>
+    <t>Jacken</t>
+  </si>
+  <si>
+    <t>Jacket</t>
+  </si>
+  <si>
+    <t>Bluse</t>
+  </si>
+  <si>
+    <t>Blusen</t>
+  </si>
+  <si>
+    <t>Blouse</t>
+  </si>
+  <si>
+    <t>Tasche</t>
+  </si>
+  <si>
+    <t>Taschen</t>
+  </si>
+  <si>
+    <t>Handbag</t>
+  </si>
+  <si>
+    <t>Mütze</t>
+  </si>
+  <si>
+    <t>Mützen</t>
+  </si>
+  <si>
+    <t>Beanie</t>
+  </si>
+  <si>
+    <t>Kravatte</t>
+  </si>
+  <si>
+    <t>Krawatten</t>
+  </si>
+  <si>
+    <t>Tie</t>
+  </si>
+  <si>
+    <t>Socke</t>
+  </si>
+  <si>
+    <t>Socken</t>
+  </si>
+  <si>
+    <t>Sock</t>
+  </si>
+  <si>
+    <t>Sandale</t>
+  </si>
+  <si>
+    <t>Sandalen</t>
+  </si>
+  <si>
+    <t>Sandal</t>
+  </si>
+  <si>
+    <t>Shorts</t>
+  </si>
+  <si>
+    <t>Short</t>
+  </si>
+  <si>
+    <t>Unterhose</t>
+  </si>
+  <si>
+    <t>Unterhosen</t>
+  </si>
+  <si>
+    <t>Underpants</t>
+  </si>
+  <si>
+    <t>Das</t>
+  </si>
+  <si>
+    <t>T-Shirt</t>
+  </si>
+  <si>
+    <t>T-Shirts</t>
+  </si>
+  <si>
+    <t>T-shirt</t>
+  </si>
+  <si>
+    <t>Hemd</t>
+  </si>
+  <si>
+    <t>Hemden</t>
+  </si>
+  <si>
+    <t>Shirt</t>
+  </si>
+  <si>
+    <t>Kleid</t>
+  </si>
+  <si>
+    <t>Kleider</t>
+  </si>
+  <si>
+    <t>Dress</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>Tops</t>
+  </si>
+  <si>
+    <t>Sweatshirt</t>
+  </si>
+  <si>
+    <t>Sweatshirts</t>
+  </si>
+  <si>
+    <t>Sakko</t>
+  </si>
+  <si>
+    <t>Sakkos</t>
+  </si>
+  <si>
+    <t>Blazer</t>
+  </si>
+  <si>
+    <t>Unterhemd</t>
+  </si>
+  <si>
+    <t>Unterhemden</t>
+  </si>
+  <si>
+    <t>Vest</t>
+  </si>
+  <si>
+    <t>Nachthemd</t>
+  </si>
+  <si>
+    <t>Nachthemden</t>
+  </si>
+  <si>
+    <t>Nightdress</t>
+  </si>
+  <si>
+    <t>Trikot</t>
+  </si>
+  <si>
+    <t>Trikots</t>
+  </si>
+  <si>
+    <t>Football tee</t>
+  </si>
+  <si>
+    <t>Kostüm</t>
+  </si>
+  <si>
+    <t>Kostüme</t>
+  </si>
+  <si>
+    <t>Costume</t>
+  </si>
+  <si>
+    <t>Accessoire</t>
+  </si>
+  <si>
+    <t>Accessoires</t>
+  </si>
+  <si>
+    <t>Accessory</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2448,24 +2333,35 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFCC0000"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF3D85C6"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF6AA84F"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2483,7 +2379,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -2522,11 +2418,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2555,6 +2466,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2564,17 +2478,263 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="37">
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2664,10 +2824,10 @@
   <tableStyles count="2">
     <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{0312DCD2-D184-4CB4-8D3F-7C5D74480270}"/>
     <tableStyle name="Nomen-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="8"/>
-      <tableStyleElement type="headerRow" dxfId="7"/>
-      <tableStyleElement type="firstRowStripe" dxfId="6"/>
-      <tableStyleElement type="secondRowStripe" dxfId="5"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="36"/>
+      <tableStyleElement type="headerRow" dxfId="35"/>
+      <tableStyleElement type="firstRowStripe" dxfId="34"/>
+      <tableStyleElement type="secondRowStripe" dxfId="33"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3055,30 +3215,30 @@
         <v>31</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3086,16 +3246,16 @@
         <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3103,16 +3263,16 @@
         <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3120,16 +3280,16 @@
         <v>26</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3137,16 +3297,16 @@
         <v>5</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3154,16 +3314,16 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3171,16 +3331,16 @@
         <v>5</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3188,16 +3348,16 @@
         <v>5</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3205,16 +3365,16 @@
         <v>5</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3222,16 +3382,16 @@
         <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3239,16 +3399,16 @@
         <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3256,33 +3416,33 @@
         <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3290,22 +3450,37 @@
         <v>5</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B22">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="32" priority="4">
       <formula>COUNTIF($B:$B, B1) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="31" priority="3">
+      <formula>COUNTIF($B:$B, C8) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12">
+    <cfRule type="expression" dxfId="30" priority="2">
+      <formula>COUNTIF($B:$B, C12) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15">
+    <cfRule type="expression" dxfId="29" priority="1">
+      <formula>COUNTIF($B:$B, C15) &gt; 1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -3344,410 +3519,410 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>421</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="E3" s="8" t="s">
         <v>425</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>426</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B4" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>429</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>430</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>432</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="E5" s="8" t="s">
         <v>433</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>436</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="E6" s="8" t="s">
         <v>437</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>438</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B7" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>440</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="E7" s="8" t="s">
         <v>441</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>442</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B8" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>444</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="E8" s="8" t="s">
         <v>445</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>446</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>448</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="E9" s="8" t="s">
         <v>449</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B10" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>452</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>453</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B12" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>456</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>457</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="E13" s="8" t="s">
         <v>460</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B14" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>463</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="E14" s="8" t="s">
         <v>464</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>467</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="E15" s="8" t="s">
         <v>468</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B16" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>471</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="E16" s="8" t="s">
         <v>472</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B17" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="D17" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="E17" s="8" t="s">
         <v>37</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B18" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>475</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="E18" s="8" t="s">
         <v>476</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>477</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>478</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>479</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="E19" s="8" t="s">
         <v>480</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B20" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>483</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="E20" s="8" t="s">
         <v>484</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>485</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B21" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>487</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="E21" s="8" t="s">
         <v>488</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>489</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B22" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>491</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="E22" s="8" t="s">
         <v>492</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>493</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B23" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="E23" s="8" t="s">
         <v>495</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>495</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>496</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" s="8" t="s">
+      <c r="D24" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="E24" s="8" t="s">
         <v>84</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>498</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B25" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="E25" s="8" t="s">
         <v>499</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>500</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -3755,16 +3930,16 @@
         <v>26</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="E26" s="5" t="s">
         <v>503</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>504</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -3772,16 +3947,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>507</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>508</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -3789,16 +3964,16 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>510</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -3806,16 +3981,16 @@
         <v>26</v>
       </c>
       <c r="B29" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>513</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="E29" s="5" t="s">
         <v>514</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>515</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -3823,16 +3998,16 @@
         <v>26</v>
       </c>
       <c r="B30" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>517</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="E30" s="5" t="s">
         <v>518</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>519</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -3840,16 +4015,16 @@
         <v>26</v>
       </c>
       <c r="B31" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>521</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>522</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -3857,16 +4032,16 @@
         <v>26</v>
       </c>
       <c r="B32" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="E32" s="5" t="s">
         <v>525</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -3874,16 +4049,16 @@
         <v>26</v>
       </c>
       <c r="B33" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="D33" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="E33" s="5" t="s">
         <v>529</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>530</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -3891,16 +4066,16 @@
         <v>26</v>
       </c>
       <c r="B34" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="D34" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="E34" s="5" t="s">
         <v>533</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>534</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -3908,14 +4083,14 @@
         <v>26</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -3923,16 +4098,16 @@
         <v>26</v>
       </c>
       <c r="B36" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="D36" s="6" t="s">
         <v>539</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="E36" s="5" t="s">
         <v>540</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>541</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -3940,16 +4115,16 @@
         <v>26</v>
       </c>
       <c r="B37" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="D37" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="E37" s="5" t="s">
         <v>544</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>545</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -3957,16 +4132,16 @@
         <v>26</v>
       </c>
       <c r="B38" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="E38" s="5" t="s">
         <v>547</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>548</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -3977,13 +4152,13 @@
         <v>31</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -3991,16 +4166,16 @@
         <v>26</v>
       </c>
       <c r="B40" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="D40" s="5" t="s">
         <v>551</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="E40" s="5" t="s">
         <v>552</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -4008,16 +4183,16 @@
         <v>26</v>
       </c>
       <c r="B41" s="5" t="s">
+        <v>553</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="E41" s="5" t="s">
         <v>556</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>557</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -4025,16 +4200,16 @@
         <v>26</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -4042,16 +4217,16 @@
         <v>26</v>
       </c>
       <c r="B43" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="E43" s="5" t="s">
         <v>560</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -4059,16 +4234,16 @@
         <v>26</v>
       </c>
       <c r="B44" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="D44" s="6" t="s">
         <v>563</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="E44" s="5" t="s">
         <v>564</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>565</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -4076,16 +4251,16 @@
         <v>26</v>
       </c>
       <c r="B45" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>44</v>
-      </c>
       <c r="D45" s="5" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -4093,16 +4268,16 @@
         <v>26</v>
       </c>
       <c r="B46" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="E46" s="5" t="s">
         <v>568</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>569</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -4110,16 +4285,16 @@
         <v>26</v>
       </c>
       <c r="B47" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="D47" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="E47" s="5" t="s">
         <v>572</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>573</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -4127,16 +4302,16 @@
         <v>26</v>
       </c>
       <c r="B48" s="5" t="s">
+        <v>573</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="D48" s="5" t="s">
         <v>575</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="E48" s="5" t="s">
         <v>576</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>577</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -4144,16 +4319,16 @@
         <v>26</v>
       </c>
       <c r="B49" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="D49" s="5" t="s">
         <v>579</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="E49" s="5" t="s">
         <v>580</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>581</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -4161,16 +4336,16 @@
         <v>26</v>
       </c>
       <c r="B50" s="5" t="s">
+        <v>581</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="D50" s="5" t="s">
         <v>583</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="E50" s="5" t="s">
         <v>584</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -4178,16 +4353,16 @@
         <v>26</v>
       </c>
       <c r="B51" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="D51" s="5" t="s">
         <v>587</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="E51" s="5" t="s">
         <v>588</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>589</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -4195,16 +4370,16 @@
         <v>26</v>
       </c>
       <c r="B52" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="D52" s="5" t="s">
         <v>591</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="E52" s="5" t="s">
         <v>592</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>593</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -4212,16 +4387,16 @@
         <v>5</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="E53" s="3" t="s">
         <v>596</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>597</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -4229,16 +4404,16 @@
         <v>5</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>599</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="E54" s="3" t="s">
         <v>600</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>601</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -4246,16 +4421,16 @@
         <v>5</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="E55" s="3" t="s">
         <v>604</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -4263,14 +4438,14 @@
         <v>5</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D56" s="3"/>
       <c r="E56" s="3" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -4278,16 +4453,16 @@
         <v>5</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="E57" s="3" t="s">
         <v>611</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>612</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -4295,16 +4470,16 @@
         <v>5</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="E58" s="3" t="s">
         <v>615</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -4312,16 +4487,16 @@
         <v>5</v>
       </c>
       <c r="B59" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="E59" s="3" t="s">
         <v>619</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -4329,16 +4504,16 @@
         <v>5</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="E60" s="3" t="s">
         <v>623</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>624</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -4346,16 +4521,16 @@
         <v>5</v>
       </c>
       <c r="B61" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>626</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="E61" s="3" t="s">
         <v>627</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>628</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -4363,16 +4538,16 @@
         <v>5</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>630</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="E62" s="3" t="s">
         <v>631</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -4380,16 +4555,16 @@
         <v>5</v>
       </c>
       <c r="B63" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="E63" s="3" t="s">
         <v>635</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>636</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -4397,16 +4572,16 @@
         <v>26</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>32</v>
+        <v>636</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -4414,16 +4589,16 @@
         <v>5</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -4431,16 +4606,16 @@
         <v>5</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="E66" s="3" t="s">
         <v>643</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -4448,16 +4623,16 @@
         <v>5</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="E67" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -4465,16 +4640,16 @@
         <v>5</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="E68" s="3" t="s">
         <v>647</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>648</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -4482,16 +4657,16 @@
         <v>5</v>
       </c>
       <c r="B69" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D69" s="4" t="s">
         <v>650</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="E69" s="3" t="s">
         <v>651</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>652</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -4499,16 +4674,16 @@
         <v>5</v>
       </c>
       <c r="B70" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="E70" s="3" t="s">
         <v>655</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>656</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -4516,16 +4691,16 @@
         <v>5</v>
       </c>
       <c r="B71" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="D71" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="E71" s="3" t="s">
         <v>659</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>660</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -4533,22 +4708,62 @@
         <v>5</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="D72" s="4" t="s">
         <v>662</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="E72" s="3" t="s">
         <v>663</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>664</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>665</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B72">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="28" priority="10">
       <formula>COUNTIF($B:$B, B1) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C10">
+    <cfRule type="expression" dxfId="27" priority="9">
+      <formula>COUNTIF($B:$B, C10) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12">
+    <cfRule type="expression" dxfId="26" priority="8">
+      <formula>COUNTIF($B:$B, C12) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C25">
+    <cfRule type="expression" dxfId="25" priority="7">
+      <formula>COUNTIF($B:$B, C25) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C28">
+    <cfRule type="expression" dxfId="24" priority="6">
+      <formula>COUNTIF($B:$B, C28) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C31">
+    <cfRule type="expression" dxfId="23" priority="5">
+      <formula>COUNTIF($B:$B, C31) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C38:C39">
+    <cfRule type="expression" dxfId="22" priority="3">
+      <formula>COUNTIF($B:$B, C38) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C46">
+    <cfRule type="expression" dxfId="21" priority="2">
+      <formula>COUNTIF($B:$B, C46) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C64">
+    <cfRule type="expression" dxfId="20" priority="1">
+      <formula>COUNTIF($B:$B, C64) &gt; 1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -4587,444 +4802,444 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>32</v>
+        <v>417</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>32</v>
+        <v>406</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>32</v>
+        <v>396</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>59</v>
+        <v>393</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>59</v>
+        <v>386</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>32</v>
+        <v>372</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>32</v>
+        <v>369</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>32</v>
+        <v>366</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>32</v>
+        <v>359</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>59</v>
+        <v>352</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>32</v>
+        <v>337</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>32</v>
+        <v>334</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -5032,16 +5247,16 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -5049,16 +5264,16 @@
         <v>26</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -5066,16 +5281,16 @@
         <v>26</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>32</v>
+        <v>323</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -5083,16 +5298,16 @@
         <v>26</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>32</v>
+        <v>321</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -5100,16 +5315,16 @@
         <v>26</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>32</v>
+        <v>318</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -5117,16 +5332,16 @@
         <v>26</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>32</v>
+        <v>315</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -5134,16 +5349,16 @@
         <v>26</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -5151,16 +5366,16 @@
         <v>26</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="39.6" x14ac:dyDescent="0.25">
@@ -5168,16 +5383,16 @@
         <v>26</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -5185,16 +5400,16 @@
         <v>26</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -5202,16 +5417,16 @@
         <v>26</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>59</v>
+        <v>297</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>297</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -5219,16 +5434,16 @@
         <v>26</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>32</v>
+        <v>294</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -5236,16 +5451,16 @@
         <v>26</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -5253,16 +5468,16 @@
         <v>26</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>32</v>
+        <v>287</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -5270,16 +5485,16 @@
         <v>26</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>32</v>
+        <v>284</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -5287,16 +5502,16 @@
         <v>26</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -5304,16 +5519,16 @@
         <v>26</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -5321,16 +5536,16 @@
         <v>26</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>32</v>
+        <v>273</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="39.6" x14ac:dyDescent="0.25">
@@ -5338,16 +5553,16 @@
         <v>26</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -5355,16 +5570,16 @@
         <v>26</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>59</v>
+        <v>266</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -5372,16 +5587,16 @@
         <v>26</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -5389,16 +5604,16 @@
         <v>26</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>59</v>
+        <v>259</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -5406,16 +5621,16 @@
         <v>26</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -5423,16 +5638,16 @@
         <v>26</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -5440,16 +5655,16 @@
         <v>26</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>32</v>
+        <v>248</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -5457,16 +5672,16 @@
         <v>26</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -5474,16 +5689,16 @@
         <v>26</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -5491,16 +5706,16 @@
         <v>26</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>32</v>
+        <v>237</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -5508,16 +5723,16 @@
         <v>26</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -5525,16 +5740,16 @@
         <v>26</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>59</v>
+        <v>230</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -5542,16 +5757,16 @@
         <v>5</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -5559,16 +5774,16 @@
         <v>5</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -5576,16 +5791,16 @@
         <v>5</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -5593,16 +5808,16 @@
         <v>5</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -5610,16 +5825,16 @@
         <v>5</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -5627,16 +5842,16 @@
         <v>5</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>59</v>
+        <v>207</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -5644,16 +5859,16 @@
         <v>5</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -5661,16 +5876,16 @@
         <v>5</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -5678,16 +5893,16 @@
         <v>5</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -5695,16 +5910,16 @@
         <v>5</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="39.6" x14ac:dyDescent="0.25">
@@ -5712,16 +5927,16 @@
         <v>5</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -5729,16 +5944,16 @@
         <v>5</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -5746,16 +5961,16 @@
         <v>5</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -5763,16 +5978,16 @@
         <v>5</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -5780,16 +5995,16 @@
         <v>5</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -5797,16 +6012,16 @@
         <v>5</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -5814,16 +6029,16 @@
         <v>5</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>59</v>
+        <v>164</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -5831,16 +6046,16 @@
         <v>5</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -5848,16 +6063,16 @@
         <v>5</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -5865,16 +6080,16 @@
         <v>5</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -5882,16 +6097,16 @@
         <v>5</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -5899,16 +6114,16 @@
         <v>5</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -5916,16 +6131,16 @@
         <v>5</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -5933,16 +6148,16 @@
         <v>5</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>59</v>
+        <v>137</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -5950,16 +6165,16 @@
         <v>5</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>59</v>
+        <v>134</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -5967,16 +6182,16 @@
         <v>5</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -5984,16 +6199,16 @@
         <v>5</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -6001,16 +6216,16 @@
         <v>5</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -6018,16 +6233,16 @@
         <v>5</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -6035,16 +6250,16 @@
         <v>5</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -6052,16 +6267,16 @@
         <v>5</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -6069,16 +6284,16 @@
         <v>5</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -6086,16 +6301,16 @@
         <v>5</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -6103,16 +6318,16 @@
         <v>5</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -6120,16 +6335,16 @@
         <v>5</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -6137,22 +6352,112 @@
         <v>5</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:B93 C37 C51 C63 C66 C75">
-    <cfRule type="expression" dxfId="2" priority="1">
+  <conditionalFormatting sqref="B1:B93 C37:C39 C51:C52 C63 C66 C74:C75">
+    <cfRule type="expression" dxfId="19" priority="28">
       <formula>COUNTIF($B:$B, B1) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2">
+    <cfRule type="expression" dxfId="18" priority="27">
+      <formula>COUNTIF($B:$B, C2) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5">
+    <cfRule type="expression" dxfId="17" priority="26">
+      <formula>COUNTIF($B:$B, C5) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:C9">
+    <cfRule type="expression" dxfId="16" priority="23">
+      <formula>COUNTIF($B:$B, C7) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C11">
+    <cfRule type="expression" dxfId="15" priority="22">
+      <formula>COUNTIF($B:$B, C11) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15:C16">
+    <cfRule type="expression" dxfId="14" priority="20">
+      <formula>COUNTIF($B:$B, C15) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18">
+    <cfRule type="expression" dxfId="13" priority="19">
+      <formula>COUNTIF($B:$B, C18) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20">
+    <cfRule type="expression" dxfId="12" priority="18">
+      <formula>COUNTIF($B:$B, C20) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C22">
+    <cfRule type="expression" dxfId="11" priority="17">
+      <formula>COUNTIF($B:$B, C22) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C26:C27">
+    <cfRule type="expression" dxfId="10" priority="15">
+      <formula>COUNTIF($B:$B, C26) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C30:C33">
+    <cfRule type="expression" dxfId="9" priority="11">
+      <formula>COUNTIF($B:$B, C30) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C41:C42">
+    <cfRule type="expression" dxfId="8" priority="9">
+      <formula>COUNTIF($B:$B, C41) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C45">
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>COUNTIF($B:$B, C45) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C47">
+    <cfRule type="expression" dxfId="6" priority="7">
+      <formula>COUNTIF($B:$B, C47) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C49">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>COUNTIF($B:$B, C49) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C55">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>COUNTIF($B:$B, C55) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C57">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>COUNTIF($B:$B, C57) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C81:C82">
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>COUNTIF($B:$B, C81) &gt; 1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C85">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>COUNTIF($B:$B, C85) &gt; 1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -6168,754 +6473,484 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A770DCFE-D96F-4C1E-AE99-BF9B1B3F6AE2}">
-  <dimension ref="A1:H21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{314FC67A-312A-4197-8A4E-59A65F06BBE2}">
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="13" t="s">
+    <row r="2" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>666</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>667</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>667</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>668</v>
       </c>
-      <c r="C2" s="13" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>666</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>669</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="C3" s="10" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B3" s="13" t="s">
+      <c r="D3" s="10" t="s">
         <v>671</v>
       </c>
-      <c r="C3" s="13" t="s">
+    </row>
+    <row r="4" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>666</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>672</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="C4" s="10" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B4" s="13" t="s">
+      <c r="D4" s="10" t="s">
         <v>674</v>
       </c>
-      <c r="C4" s="13" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
+        <v>666</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="C5" s="10" t="s">
         <v>676</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B5" s="13" t="s">
+      <c r="D5" s="10" t="s">
         <v>677</v>
       </c>
-      <c r="C5" s="13" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
+        <v>666</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>678</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="C6" s="10" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="13" t="s">
+      <c r="D6" s="10" t="s">
         <v>680</v>
       </c>
-      <c r="C6" s="13" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
+        <v>666</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>681</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="C7" s="10" t="s">
+        <v>681</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>682</v>
       </c>
-      <c r="H6" s="14" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="13" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>666</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>683</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C8" s="10" t="s">
         <v>684</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D8" s="10" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="13" t="s">
+    <row r="9" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
+        <v>666</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>686</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C9" s="10" t="s">
         <v>687</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D9" s="10" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9" s="13" t="s">
+    <row r="10" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
+        <v>666</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>689</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C10" s="10" t="s">
         <v>690</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D10" s="10" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="13" t="s">
+    <row r="11" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
+        <v>666</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>692</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C11" s="10" t="s">
+        <v>692</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>693</v>
       </c>
-      <c r="D10" s="13" t="s">
+    </row>
+    <row r="12" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
+        <v>666</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="13" t="s">
+      <c r="C12" s="10" t="s">
         <v>695</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="D12" s="10" t="s">
         <v>696</v>
       </c>
-      <c r="D11" s="13" t="s">
+    </row>
+    <row r="13" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="13" t="s">
+      <c r="B13" s="10" t="s">
         <v>698</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C13" s="10" t="s">
         <v>699</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D13" s="10" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="13" t="s">
+    <row r="14" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>701</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C14" s="10" t="s">
+        <v>701</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>702</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="C15" s="10" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="13" t="s">
+      <c r="D15" s="10" t="s">
         <v>704</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>704</v>
-      </c>
-      <c r="D14" s="13" t="s">
+    </row>
+    <row r="16" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="13" t="s">
+      <c r="C16" s="10" t="s">
         <v>706</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="D16" s="10" t="s">
         <v>707</v>
       </c>
-      <c r="D15" s="13" t="s">
+    </row>
+    <row r="17" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="13" t="s">
+      <c r="C17" s="10" t="s">
         <v>709</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="D17" s="10" t="s">
         <v>710</v>
       </c>
-      <c r="D16" s="13" t="s">
+    </row>
+    <row r="18" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>711</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="13" t="s">
+      <c r="C18" s="10" t="s">
         <v>712</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>712</v>
-      </c>
-      <c r="D17" s="13" t="s">
+      <c r="D18" s="10" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B18" s="13" t="s">
+    <row r="19" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="B19" s="10" t="s">
         <v>714</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C19" s="10" t="s">
         <v>715</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D19" s="10" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B19" s="13" t="s">
+    <row r="20" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>717</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>717</v>
-      </c>
-      <c r="D19" s="13" t="s">
+      <c r="C20" s="10" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="13" t="s">
+      <c r="D20" s="10" t="s">
         <v>719</v>
       </c>
-      <c r="C20" s="13" t="s">
+    </row>
+    <row r="21" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="B21" s="10" t="s">
         <v>720</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="C21" s="10" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="13" t="s">
+      <c r="D21" s="10" t="s">
         <v>722</v>
       </c>
-      <c r="C21" s="13" t="s">
+    </row>
+    <row r="22" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>723</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="C22" s="10" t="s">
+        <v>723</v>
+      </c>
+      <c r="D22" s="10" t="s">
         <v>724</v>
       </c>
     </row>
-  </sheetData>
-  <conditionalFormatting sqref="B1">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>COUNTIF($B:$B, B1) &gt; 1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{103D9FBD-A1E9-41B6-85A9-3259ACE60150}">
-  <dimension ref="A1:D31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>499</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>499</v>
-      </c>
-      <c r="D2" s="13" t="s">
+    <row r="23" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>725</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B3" s="13" t="s">
+      <c r="C23" s="10" t="s">
         <v>726</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>726</v>
-      </c>
-      <c r="D3" s="13" t="s">
+      <c r="D23" s="10" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B4" s="13" t="s">
+    <row r="24" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
         <v>728</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="B24" s="10" t="s">
+        <v>729</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>730</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="10" t="s">
         <v>728</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>730</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>731</v>
-      </c>
-      <c r="D5" s="13" t="s">
+      <c r="B25" s="10" t="s">
         <v>732</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B6" s="13" t="s">
+      <c r="C25" s="10" t="s">
         <v>733</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>733</v>
-      </c>
-      <c r="D6" s="13" t="s">
+      <c r="D25" s="10" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B7" s="13" t="s">
+    <row r="26" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="10" t="s">
+        <v>728</v>
+      </c>
+      <c r="B26" s="10" t="s">
         <v>735</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>735</v>
-      </c>
-      <c r="D7" s="13" t="s">
+      <c r="C26" s="10" t="s">
         <v>736</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="13" t="s">
+      <c r="D26" s="10" t="s">
         <v>737</v>
       </c>
-      <c r="C8" s="13" t="s">
+    </row>
+    <row r="27" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="10" t="s">
+        <v>728</v>
+      </c>
+      <c r="B27" s="10" t="s">
         <v>738</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="C27" s="10" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="13" t="s">
+      <c r="D27" s="10" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="10" t="s">
+        <v>728</v>
+      </c>
+      <c r="B28" s="10" t="s">
         <v>740</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C28" s="10" t="s">
         <v>741</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D28" s="10" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="10" t="s">
+        <v>728</v>
+      </c>
+      <c r="B29" s="10" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="13" t="s">
+      <c r="C29" s="10" t="s">
         <v>743</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="D29" s="10" t="s">
         <v>744</v>
       </c>
-      <c r="D10" s="13" t="s">
+    </row>
+    <row r="30" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="10" t="s">
+        <v>728</v>
+      </c>
+      <c r="B30" s="10" t="s">
         <v>745</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="13" t="s">
+      <c r="C30" s="10" t="s">
         <v>746</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>746</v>
-      </c>
-      <c r="D11" s="13" t="s">
+      <c r="D30" s="10" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>583</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>584</v>
-      </c>
-      <c r="D12" s="13" t="s">
+    <row r="31" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="10" t="s">
+        <v>728</v>
+      </c>
+      <c r="B31" s="10" t="s">
         <v>748</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>575</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>576</v>
-      </c>
-      <c r="D13" s="13" t="s">
+      <c r="C31" s="10" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="13" t="s">
+      <c r="D31" s="10" t="s">
         <v>750</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>750</v>
-      </c>
-      <c r="D14" s="13" t="s">
+    </row>
+    <row r="32" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="10" t="s">
+        <v>728</v>
+      </c>
+      <c r="B32" s="10" t="s">
         <v>751</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B15" s="13" t="s">
+      <c r="C32" s="10" t="s">
         <v>752</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="D32" s="10" t="s">
         <v>753</v>
       </c>
-      <c r="D15" s="13" t="s">
+    </row>
+    <row r="33" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="10" t="s">
+        <v>728</v>
+      </c>
+      <c r="B33" s="10" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B16" s="13" t="s">
+      <c r="C33" s="10" t="s">
         <v>755</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="D33" s="10" t="s">
         <v>756</v>
       </c>
-      <c r="D16" s="13" t="s">
+    </row>
+    <row r="34" spans="1:4" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="10" t="s">
+        <v>728</v>
+      </c>
+      <c r="B34" s="10" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="13" t="s">
+      <c r="C34" s="10" t="s">
         <v>758</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="D34" s="10" t="s">
         <v>759</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>761</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>762</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>764</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>765</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>424</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>425</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>768</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>769</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>771</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>772</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>774</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>774</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>776</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>776</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>778</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>779</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>781</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>781</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>783</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>784</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>786</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>787</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>789</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>790</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>792</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>793</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>795</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>796</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>797</v>
       </c>
     </row>
   </sheetData>
